--- a/uploads/Template_Import_Journal.xlsx
+++ b/uploads/Template_Import_Journal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/def358f71f484966/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\acv-master\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D1CD086-F7B7-4F04-A356-E00C4A849048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61157CF6-4FFC-47DC-B08A-834B60AF4143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F1E41195-A436-4E53-BFEC-2E2372664A99}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>journal_date</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>Description 2</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>new</t>
   </si>
 </sst>
 </file>
@@ -119,7 +125,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -142,12 +148,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -159,6 +178,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -496,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{588D8980-4538-435A-8B4C-FDDA97F3307D}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="3" customWidth="1"/>
@@ -510,7 +532,7 @@
     <col min="9" max="9" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -535,8 +557,11 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>44562</v>
       </c>
@@ -561,8 +586,11 @@
       <c r="H2" s="1">
         <v>50000</v>
       </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>44563</v>
       </c>
@@ -587,8 +615,11 @@
       <c r="H3" s="1">
         <v>150000</v>
       </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>

--- a/uploads/Template_Import_Journal.xlsx
+++ b/uploads/Template_Import_Journal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\acv-master\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61157CF6-4FFC-47DC-B08A-834B60AF4143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06698D2A-B4A0-4400-A0ED-8622AC1C7F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F1E41195-A436-4E53-BFEC-2E2372664A99}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>journal_date</t>
   </si>
@@ -90,6 +90,27 @@
   </si>
   <si>
     <t>new</t>
+  </si>
+  <si>
+    <t>NPWP</t>
+  </si>
+  <si>
+    <t>SUPPLIER</t>
+  </si>
+  <si>
+    <t>INVOICE NUMBER</t>
+  </si>
+  <si>
+    <t>INVOICE DATE</t>
+  </si>
+  <si>
+    <t>0702213539016000</t>
+  </si>
+  <si>
+    <t>PT. Berlian Amal Perkasa</t>
+  </si>
+  <si>
+    <t>RC060C9-2014</t>
   </si>
 </sst>
 </file>
@@ -112,7 +133,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -124,8 +145,14 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -161,12 +188,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -182,6 +237,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -518,21 +582,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{588D8980-4538-435A-8B4C-FDDA97F3307D}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="3" customWidth="1"/>
     <col min="2" max="2" width="15" style="3" customWidth="1"/>
     <col min="3" max="3" width="12" style="3" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="17.28515625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -545,23 +611,35 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>44562</v>
       </c>
@@ -574,23 +652,35 @@
       <c r="D2" s="1">
         <v>1001</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="8">
+        <v>45931</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1">
+      <c r="K2" s="1">
         <v>100000</v>
       </c>
-      <c r="H2" s="1">
+      <c r="L2" s="1">
         <v>50000</v>
       </c>
-      <c r="I2" t="s">
+      <c r="M2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>44563</v>
       </c>
@@ -603,31 +693,197 @@
       <c r="D3" s="1">
         <v>1002</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="8">
+        <v>45931</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="1">
+      <c r="K3" s="1">
         <v>200000</v>
       </c>
-      <c r="H3" s="1">
+      <c r="L3" s="1">
         <v>150000</v>
       </c>
-      <c r="I3" t="s">
+      <c r="M3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
